--- a/output/Tables/Modal shift/HIA_modal_shift_Rubin_1000replicate.xlsx
+++ b/output/Tables/Modal shift/HIA_modal_shift_Rubin_1000replicate.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>70264.197</v>
+        <v>66448.408</v>
       </c>
       <c r="C2">
-        <v>66828.175</v>
+        <v>63079.68</v>
       </c>
       <c r="D2">
-        <v>73700.21799999999</v>
+        <v>69817.13499999999</v>
       </c>
       <c r="E2">
-        <v>721719.487</v>
+        <v>681323.174</v>
       </c>
       <c r="F2">
-        <v>701648.311</v>
+        <v>661677.6</v>
       </c>
       <c r="G2">
-        <v>741790.662</v>
+        <v>700968.748</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>95988691705.438</v>
+        <v>90615982091.853</v>
       </c>
       <c r="L2">
-        <v>93319225378.605</v>
+        <v>88003120750.937</v>
       </c>
       <c r="M2">
-        <v>98658158032.271</v>
+        <v>93228843432.769</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>49987.962</v>
+        <v>46164.698</v>
       </c>
       <c r="C3">
-        <v>47910.422</v>
+        <v>44179.034</v>
       </c>
       <c r="D3">
-        <v>52065.502</v>
+        <v>48150.362</v>
       </c>
       <c r="E3">
-        <v>44517.872</v>
+        <v>63340.166</v>
       </c>
       <c r="F3">
-        <v>42872.975</v>
+        <v>60882.793</v>
       </c>
       <c r="G3">
-        <v>46162.769</v>
+        <v>65797.538</v>
       </c>
       <c r="H3">
-        <v>2784429483.902</v>
+        <v>2432648764.766</v>
       </c>
       <c r="I3">
-        <v>2668706349.701</v>
+        <v>2328014182.421</v>
       </c>
       <c r="J3">
-        <v>2900152618.102</v>
+        <v>2537283347.112</v>
       </c>
       <c r="K3">
-        <v>5920877006.444</v>
+        <v>8424242020.559</v>
       </c>
       <c r="L3">
-        <v>5702105697.778</v>
+        <v>8097411455.682</v>
       </c>
       <c r="M3">
-        <v>6139648315.109</v>
+        <v>8751072585.436001</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>39877.561</v>
+        <v>10760.176</v>
       </c>
       <c r="C4">
-        <v>38129.83</v>
+        <v>10212.916</v>
       </c>
       <c r="D4">
-        <v>41625.292</v>
+        <v>11307.437</v>
       </c>
       <c r="E4">
-        <v>60161.544</v>
+        <v>5055.752</v>
       </c>
       <c r="F4">
-        <v>56879.905</v>
+        <v>4816.123</v>
       </c>
       <c r="G4">
-        <v>63443.183</v>
+        <v>5295.381</v>
       </c>
       <c r="H4">
-        <v>590467046.008</v>
+        <v>315477608.42</v>
       </c>
       <c r="I4">
-        <v>564588396.247</v>
+        <v>299432475.052</v>
       </c>
       <c r="J4">
-        <v>616345695.77</v>
+        <v>331522741.788</v>
       </c>
       <c r="K4">
-        <v>8001485412.334</v>
+        <v>672415036.6390001</v>
       </c>
       <c r="L4">
-        <v>7565027429.228</v>
+        <v>640544377.808</v>
       </c>
       <c r="M4">
-        <v>8437943395.44</v>
+        <v>704285695.47</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>8147.728</v>
+        <v>7409.5</v>
       </c>
       <c r="C5">
-        <v>7780.709</v>
+        <v>7093.342</v>
       </c>
       <c r="D5">
-        <v>8514.746999999999</v>
+        <v>7725.658</v>
       </c>
       <c r="E5">
-        <v>15904.959</v>
+        <v>13501.932</v>
       </c>
       <c r="F5">
-        <v>15154.036</v>
+        <v>12886.162</v>
       </c>
       <c r="G5">
-        <v>16655.882</v>
+        <v>14117.701</v>
       </c>
       <c r="H5">
-        <v>612717287.002</v>
+        <v>290459798.08</v>
       </c>
       <c r="I5">
-        <v>585117070.2819999</v>
+        <v>278066087.024</v>
       </c>
       <c r="J5">
-        <v>640317503.723</v>
+        <v>302853509.135</v>
       </c>
       <c r="K5">
-        <v>2115359531.81</v>
+        <v>1795756943.574</v>
       </c>
       <c r="L5">
-        <v>2015486743.189</v>
+        <v>1713859610.284</v>
       </c>
       <c r="M5">
-        <v>2215232320.43</v>
+        <v>1877654276.864</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>17395.1</v>
+        <v>15635.982</v>
       </c>
       <c r="C6">
-        <v>16366.987</v>
+        <v>14683.878</v>
       </c>
       <c r="D6">
-        <v>18423.213</v>
+        <v>16588.087</v>
       </c>
       <c r="E6">
-        <v>28772.754</v>
+        <v>17832.305</v>
       </c>
       <c r="F6">
-        <v>27424.701</v>
+        <v>16721.135</v>
       </c>
       <c r="G6">
-        <v>30120.807</v>
+        <v>18943.475</v>
       </c>
       <c r="H6">
-        <v>292916091.58</v>
+        <v>260307832.715</v>
       </c>
       <c r="I6">
-        <v>275603701.612</v>
+        <v>244457193.743</v>
       </c>
       <c r="J6">
-        <v>310228481.547</v>
+        <v>276158471.687</v>
       </c>
       <c r="K6">
-        <v>3826776300.53</v>
+        <v>2371696579.088</v>
       </c>
       <c r="L6">
-        <v>3647485212.179</v>
+        <v>2223910939.77</v>
       </c>
       <c r="M6">
-        <v>4006067388.88</v>
+        <v>2519482218.406</v>
       </c>
     </row>
     <row r="7">
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>159363.809</v>
+        <v>163179.974</v>
       </c>
       <c r="C7">
-        <v>153780.265</v>
+        <v>157393.911</v>
       </c>
       <c r="D7">
-        <v>164947.353</v>
+        <v>168966.037</v>
       </c>
       <c r="E7">
-        <v>51684.463</v>
+        <v>61009.111</v>
       </c>
       <c r="F7">
-        <v>49173.121</v>
+        <v>58183.072</v>
       </c>
       <c r="G7">
-        <v>54195.806</v>
+        <v>63835.149</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,56 +670,56 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>6874033644.604</v>
+        <v>8114211743.778</v>
       </c>
       <c r="L7">
-        <v>6540025147.983</v>
+        <v>7738348615.724</v>
       </c>
       <c r="M7">
-        <v>7208042141.226</v>
+        <v>8490074871.831</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>Chronic diseases</t>
         </is>
       </c>
       <c r="B8">
-        <v>274772.16</v>
+        <v>79970.356</v>
       </c>
       <c r="C8">
-        <v>263968.213</v>
+        <v>76169.17</v>
       </c>
       <c r="D8">
-        <v>285576.107</v>
+        <v>83771.54399999999</v>
       </c>
       <c r="E8">
-        <v>201041.592</v>
+        <v>99730.155</v>
       </c>
       <c r="F8">
-        <v>191504.738</v>
+        <v>95306.21299999999</v>
       </c>
       <c r="G8">
-        <v>210578.447</v>
+        <v>104154.095</v>
       </c>
       <c r="H8">
-        <v>4280529908.492</v>
+        <v>3298894003.981</v>
       </c>
       <c r="I8">
-        <v>4094015517.842</v>
+        <v>3149969938.24</v>
       </c>
       <c r="J8">
-        <v>4467044299.142</v>
+        <v>3447818069.722</v>
       </c>
       <c r="K8">
-        <v>26738531895.722</v>
+        <v>13264110579.86</v>
       </c>
       <c r="L8">
-        <v>25470130230.357</v>
+        <v>12675726383.544</v>
       </c>
       <c r="M8">
-        <v>28006933561.085</v>
+        <v>13852494776.176</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>345036.357</v>
+        <v>309598.738</v>
       </c>
       <c r="C9">
-        <v>330796.388</v>
+        <v>296642.761</v>
       </c>
       <c r="D9">
-        <v>359276.325</v>
+        <v>322554.716</v>
       </c>
       <c r="E9">
-        <v>922761.0789999999</v>
+        <v>842062.4400000001</v>
       </c>
       <c r="F9">
-        <v>893153.049</v>
+        <v>815166.885</v>
       </c>
       <c r="G9">
-        <v>952369.1089999999</v>
+        <v>868957.9920000001</v>
       </c>
       <c r="H9">
-        <v>4280529908.492</v>
+        <v>3298894003.981</v>
       </c>
       <c r="I9">
-        <v>4094015517.842</v>
+        <v>3149969938.24</v>
       </c>
       <c r="J9">
-        <v>4467044299.142</v>
+        <v>3447818069.722</v>
       </c>
       <c r="K9">
-        <v>122727223601.16</v>
+        <v>111994304415.491</v>
       </c>
       <c r="L9">
-        <v>118789355608.962</v>
+        <v>108417195750.205</v>
       </c>
       <c r="M9">
-        <v>126665091593.356</v>
+        <v>115571413080.776</v>
       </c>
     </row>
   </sheetData>
